--- a/virtual-physics-lab/app/dl/EJC_Q3_rod_moments.xlsx
+++ b/virtual-physics-lab/app/dl/EJC_Q3_rod_moments.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,9 +101,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -191,7 +194,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>τ_Q against τ_P</a:t>
+              <a:t>τQ against τP</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -258,7 +261,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>τ_P / N m</a:t>
+                  <a:t>τP / N m</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -285,7 +288,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>τ_Q / N m</a:t>
+                  <a:t>τQ / N m</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -637,7 +640,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>S = 80.0 cm, θ = 50°, W = 0.0981 N, F = 2.94 N. Compute τ_P = 5Wp and τ_Q = 7Wq, then plot τ_Q against τ_P.</t>
+          <t>S = 80.0 cm, θ = 50°, W = 0.0981 N, F = 2.94 N. Compute τP = 5Wp and τQ = 7Wq, then plot τQ against τP.</t>
         </is>
       </c>
     </row>
@@ -661,12 +664,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>τ_P / N m</t>
+          <t>τP / N m</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>τ_Q / N m</t>
+          <t>τQ / N m</t>
         </is>
       </c>
     </row>
@@ -780,12 +783,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>τ_P / N m</t>
+          <t>τP / N m</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>τ_Q / N m</t>
+          <t>τQ / N m</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -819,7 +822,7 @@
         <f>7*0.0981*A6/100</f>
         <v/>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>B = gradient</t>
         </is>
@@ -828,7 +831,7 @@
         <f>SLOPE(D6:D11,C6:C11)</f>
         <v/>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -845,7 +848,7 @@
         <f>7*0.0981*A7/100</f>
         <v/>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>A = intercept</t>
         </is>
@@ -854,7 +857,7 @@
         <f>INTERCEPT(D6:D11,C6:C11)</f>
         <v/>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>N m</t>
         </is>
@@ -875,7 +878,7 @@
         <f>7*0.0981*A8/100</f>
         <v/>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>R = F sinθ − 2A/S</t>
         </is>
@@ -884,7 +887,7 @@
         <f>2.94*SIN(RADIANS(50))-2*INTERCEPT(D6:D11,C6:C11)/0.8</f>
         <v/>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
